--- a/Sample/LabourSummary/HGRH開工人數表.xlsx
+++ b/Sample/LabourSummary/HGRH開工人數表.xlsx
@@ -13906,7 +13906,7 @@
       </c>
       <c r="D13" s="14"/>
       <c r="E13" s="15">
-        <v>333</v>
+        <v>6</v>
       </c>
       <c r="F13" s="15"/>
       <c r="G13" s="15"/>
